--- a/src/data/calibration_data_orange.xlsx
+++ b/src/data/calibration_data_orange.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Tan\Documents\ECSE211\ECSE211_W26_Final_Project\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7F9A61A6-6C3A-4287-B1C2-021F93164D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4B7BA2-0D44-4FAB-BFF9-BEAE34D0823F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A6FBE27-17BE-408B-9A85-2B7E5A10F943}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_data_orange" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>R</t>
   </si>
@@ -31,10 +44,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>vector avg</t>
   </si>
   <si>
-    <t>std dev</t>
+    <t>vector std dev</t>
+  </si>
+  <si>
+    <t>ratio avg</t>
+  </si>
+  <si>
+    <t>ratio std dev</t>
   </si>
 </sst>
 </file>
@@ -895,10 +914,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C6DD43-07D3-434A-9131-A72F1CC725EC}">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -909,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>67</v>
       </c>
@@ -931,23 +950,35 @@
         <f t="shared" si="0"/>
         <v>2.728264823572208E-3</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <f>A2/($A2+$B2+$C2)</f>
+        <v>0.60909090909090913</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:K2" si="1">B2/($A2+$B2+$C2)</f>
+        <v>0.25454545454545452</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="1"/>
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="M2" t="s">
         <v>3</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <f>AVERAGE(E2:E87)</f>
         <v>1.2555843779940561E-2</v>
       </c>
-      <c r="K2">
+      <c r="O2">
         <f>AVERAGE(F2:F87)</f>
         <v>4.8911672472052034E-3</v>
       </c>
-      <c r="L2">
+      <c r="P2">
         <f>AVERAGE(G2:G87)</f>
         <v>2.5177349411317175E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>67</v>
       </c>
@@ -958,34 +989,46 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E66" si="1">A3/($A3^2 + $B3^2 + $C3^2)</f>
+        <f t="shared" ref="E3:E66" si="2">A3/($A3^2 + $B3^2 + $C3^2)</f>
         <v>1.2437349173937256E-2</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F66" si="2">B3/($A3^2 + $B3^2 + $C3^2)</f>
+        <f t="shared" ref="F3:F66" si="3">B3/($A3^2 + $B3^2 + $C3^2)</f>
         <v>5.0120660850194914E-3</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G66" si="3">C3/($A3^2 + $B3^2 + $C3^2)</f>
+        <f t="shared" ref="G3:G66" si="4">C3/($A3^2 + $B3^2 + $C3^2)</f>
         <v>2.4132170038982737E-3</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="5">A3/($A3+$B3+$C3)</f>
+        <v>0.62616822429906538</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="6">B3/($A3+$B3+$C3)</f>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="7">C3/($A3+$B3+$C3)</f>
+        <v>0.12149532710280374</v>
+      </c>
+      <c r="M3" t="s">
         <v>4</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <f>_xlfn.STDEV.P(E2:E87)</f>
         <v>3.7584481270872683E-4</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:L3" si="4">_xlfn.STDEV.P(F2:F87)</f>
+      <c r="O3">
+        <f>_xlfn.STDEV.P(F2:F87)</f>
         <v>2.0988215729589383E-4</v>
       </c>
-      <c r="L3">
-        <f t="shared" si="4"/>
+      <c r="P3">
+        <f>_xlfn.STDEV.P(G2:G87)</f>
         <v>2.2029451365589465E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>66</v>
       </c>
@@ -996,19 +1039,31 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2624330527926549E-2</v>
       </c>
       <c r="F4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9732211170619737E-3</v>
       </c>
       <c r="G4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6778882938026014E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="5"/>
+        <v>0.62264150943396224</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="6"/>
+        <v>0.24528301886792453</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="7"/>
+        <v>0.13207547169811321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>67</v>
       </c>
@@ -1019,19 +1074,46 @@
         <v>13</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2437349173937256E-2</v>
       </c>
       <c r="F5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0120660850194914E-3</v>
       </c>
       <c r="G5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4132170038982737E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="5"/>
+        <v>0.62616822429906538</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="7"/>
+        <v>0.12149532710280374</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>AVERAGE(I2:I87)</f>
+        <v>0.62887911920721062</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:P5" si="8">AVERAGE(J2:J87)</f>
+        <v>0.24494592403032175</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="8"/>
+        <v>0.1261749567624674</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>63</v>
       </c>
@@ -1042,19 +1124,46 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3618677042801557E-2</v>
       </c>
       <c r="F6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1880674448767832E-3</v>
       </c>
       <c r="G6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9455252918287938E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="5"/>
+        <v>0.65625</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="7"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="M6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.STDEV.P(I2:I87)</f>
+        <v>1.0417870964799585E-2</v>
+      </c>
+      <c r="O6">
+        <f t="shared" ref="O6:P6" si="9">_xlfn.STDEV.P(J2:J87)</f>
+        <v>7.4803104058616537E-3</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="9"/>
+        <v>1.130649476465694E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>65</v>
       </c>
@@ -1065,19 +1174,31 @@
         <v>13</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2950787009364416E-2</v>
       </c>
       <c r="F7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9810719266786211E-3</v>
       </c>
       <c r="G7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5901574018728831E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="5"/>
+        <v>0.6310679611650486</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="7"/>
+        <v>0.12621359223300971</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>65</v>
       </c>
@@ -1088,19 +1209,31 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2950787009364416E-2</v>
       </c>
       <c r="F8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9810719266786211E-3</v>
       </c>
       <c r="G8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5901574018728831E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="5"/>
+        <v>0.6310679611650486</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="7"/>
+        <v>0.12621359223300971</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>66</v>
       </c>
@@ -1111,19 +1244,31 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2301957129543337E-2</v>
       </c>
       <c r="F9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.2190121155638401E-3</v>
       </c>
       <c r="G9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7958993476234857E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="5"/>
+        <v>0.60550458715596334</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="6"/>
+        <v>0.25688073394495414</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>0.13761467889908258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>66</v>
       </c>
@@ -1134,19 +1279,31 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2878048780487804E-2</v>
       </c>
       <c r="F10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8780487804878049E-3</v>
       </c>
       <c r="G10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3414634146341463E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="7"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>67</v>
       </c>
@@ -1157,19 +1314,31 @@
         <v>13</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2437349173937256E-2</v>
       </c>
       <c r="F11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0120660850194914E-3</v>
       </c>
       <c r="G11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4132170038982737E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.62616822429906538</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="7"/>
+        <v>0.12149532710280374</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>65</v>
       </c>
@@ -1180,19 +1349,31 @@
         <v>12</v>
       </c>
       <c r="E12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.288404360753221E-2</v>
       </c>
       <c r="F12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1536174430128843E-3</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3785926660059467E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0.6310679611650486</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="6"/>
+        <v>0.25242718446601942</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="7"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>67</v>
       </c>
@@ -1203,19 +1384,31 @@
         <v>12</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2620079110943681E-2</v>
       </c>
       <c r="F13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.89734413260501E-3</v>
       </c>
       <c r="G13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.260312676586928E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0.63809523809523805</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="7"/>
+        <v>0.11428571428571428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>66</v>
       </c>
@@ -1226,19 +1419,31 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2878048780487804E-2</v>
       </c>
       <c r="F14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8780487804878049E-3</v>
       </c>
       <c r="G14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3414634146341463E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="7"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>67</v>
       </c>
@@ -1249,19 +1454,31 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2250868531724263E-2</v>
       </c>
       <c r="F15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1197659535564093E-3</v>
       </c>
       <c r="G15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5598829767782046E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0.61467889908256879</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="6"/>
+        <v>0.25688073394495414</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="7"/>
+        <v>0.12844036697247707</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>65</v>
       </c>
@@ -1272,19 +1489,31 @@
         <v>13</v>
       </c>
       <c r="E16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.282051282051282E-2</v>
       </c>
       <c r="F16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1282051282051282E-3</v>
       </c>
       <c r="G16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5641025641025641E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>66</v>
       </c>
@@ -1295,19 +1524,31 @@
         <v>12</v>
       </c>
       <c r="E17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2751159196290572E-2</v>
       </c>
       <c r="F17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0231839258114376E-3</v>
       </c>
       <c r="G17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3183925811437402E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="5"/>
+        <v>0.63461538461538458</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="7"/>
+        <v>0.11538461538461539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>66</v>
       </c>
@@ -1318,19 +1559,31 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2497633024048476E-2</v>
       </c>
       <c r="F18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1126680552925586E-3</v>
       </c>
       <c r="G18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6510130657072524E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="5"/>
+        <v>0.61682242990654201</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="7"/>
+        <v>0.13084112149532709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>67</v>
       </c>
@@ -1341,19 +1594,31 @@
         <v>12</v>
       </c>
       <c r="E19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2495337560611712E-2</v>
       </c>
       <c r="F19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0354345393509884E-3</v>
       </c>
       <c r="G19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.237970906378217E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="5"/>
+        <v>0.63207547169811318</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="6"/>
+        <v>0.25471698113207547</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="7"/>
+        <v>0.11320754716981132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>66</v>
       </c>
@@ -1364,19 +1629,31 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2497633024048476E-2</v>
       </c>
       <c r="F20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1126680552925586E-3</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6510130657072524E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0.61682242990654201</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="7"/>
+        <v>0.13084112149532709</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>67</v>
       </c>
@@ -1387,19 +1664,31 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2375323236054673E-2</v>
       </c>
       <c r="F21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9870705578130775E-3</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5858884373845584E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>0.62037037037037035</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="7"/>
+        <v>0.12962962962962962</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>64</v>
       </c>
@@ -1410,19 +1699,31 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3275254096660444E-2</v>
       </c>
       <c r="F22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1856461315079863E-3</v>
       </c>
       <c r="G22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.0742584526031943E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>0.64646464646464652</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>0.25252525252525254</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="7"/>
+        <v>0.10101010101010101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>65</v>
       </c>
@@ -1433,19 +1734,31 @@
         <v>13</v>
       </c>
       <c r="E23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2950787009364416E-2</v>
       </c>
       <c r="F23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9810719266786211E-3</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5901574018728831E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>0.6310679611650486</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="7"/>
+        <v>0.12621359223300971</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>65</v>
       </c>
@@ -1456,19 +1769,31 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2752599568373553E-2</v>
       </c>
       <c r="F24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1010398273494215E-3</v>
       </c>
       <c r="G24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7467137531881499E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="5"/>
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="7"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>65</v>
       </c>
@@ -1479,19 +1804,31 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2881490289338089E-2</v>
       </c>
       <c r="F25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9544193420531114E-3</v>
       </c>
       <c r="G25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7744748315497426E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="6"/>
+        <v>0.24038461538461539</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="7"/>
+        <v>0.13461538461538461</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>66</v>
       </c>
@@ -1502,19 +1839,31 @@
         <v>12</v>
       </c>
       <c r="E26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2878048780487804E-2</v>
       </c>
       <c r="F26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8780487804878049E-3</v>
       </c>
       <c r="G26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3414634146341463E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="7"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>67</v>
       </c>
@@ -1525,19 +1874,31 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2497668345457937E-2</v>
       </c>
       <c r="F27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8498414474911393E-3</v>
       </c>
       <c r="G27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6114530871106136E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>0.62616822429906538</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="6"/>
+        <v>0.24299065420560748</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>0.13084112149532709</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>67</v>
       </c>
@@ -1548,19 +1909,31 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2250868531724263E-2</v>
       </c>
       <c r="F28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1197659535564093E-3</v>
       </c>
       <c r="G28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5598829767782046E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <f t="shared" si="5"/>
+        <v>0.61467889908256879</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>0.25688073394495414</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="7"/>
+        <v>0.12844036697247707</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>65</v>
       </c>
@@ -1571,19 +1944,31 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2752599568373553E-2</v>
       </c>
       <c r="F29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1010398273494215E-3</v>
       </c>
       <c r="G29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7467137531881499E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <f t="shared" si="5"/>
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="7"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>64</v>
       </c>
@@ -1594,19 +1979,31 @@
         <v>12</v>
       </c>
       <c r="E30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.31551901336074E-2</v>
       </c>
       <c r="F30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1387461459403904E-3</v>
       </c>
       <c r="G30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4665981500513875E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <f t="shared" si="5"/>
+        <v>0.63366336633663367</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="6"/>
+        <v>0.24752475247524752</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="7"/>
+        <v>0.11881188118811881</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>66</v>
       </c>
@@ -1617,19 +2014,31 @@
         <v>11</v>
       </c>
       <c r="E31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2936103488827911E-2</v>
       </c>
       <c r="F31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9000392003136026E-3</v>
       </c>
       <c r="G31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1560172481379851E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <f t="shared" si="5"/>
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="6"/>
+        <v>0.24509803921568626</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="7"/>
+        <v>0.10784313725490197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>67</v>
       </c>
@@ -1640,19 +2049,31 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2375323236054673E-2</v>
       </c>
       <c r="F32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9870705578130775E-3</v>
       </c>
       <c r="G32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5858884373845584E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <f t="shared" si="5"/>
+        <v>0.62037037037037035</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="7"/>
+        <v>0.12962962962962962</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>68</v>
       </c>
@@ -1663,19 +2084,31 @@
         <v>12</v>
       </c>
       <c r="E33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2370383845734037E-2</v>
       </c>
       <c r="F33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9117700563943972E-3</v>
       </c>
       <c r="G33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1830089139530653E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <f t="shared" si="5"/>
+        <v>0.63551401869158874</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="7"/>
+        <v>0.11214953271028037</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>68</v>
       </c>
@@ -1686,19 +2119,31 @@
         <v>13</v>
       </c>
       <c r="E34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.231437884824339E-2</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8895327779789931E-3</v>
       </c>
       <c r="G34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3542194856935894E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <f t="shared" si="5"/>
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="7"/>
+        <v>0.12037037037037036</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>67</v>
       </c>
@@ -1709,19 +2154,31 @@
         <v>12</v>
       </c>
       <c r="E35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2620079110943681E-2</v>
       </c>
       <c r="F35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.89734413260501E-3</v>
       </c>
       <c r="G35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.260312676586928E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <f t="shared" si="5"/>
+        <v>0.63809523809523805</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="7"/>
+        <v>0.11428571428571428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>68</v>
       </c>
@@ -1732,19 +2189,31 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2012012012012012E-2</v>
       </c>
       <c r="F36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1227698286521817E-3</v>
       </c>
       <c r="G36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4730612965907085E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <f t="shared" si="5"/>
+        <v>0.61261261261261257</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="6"/>
+        <v>0.26126126126126126</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="7"/>
+        <v>0.12612612612612611</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>64</v>
       </c>
@@ -1755,19 +2224,31 @@
         <v>12</v>
       </c>
       <c r="E37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.31551901336074E-2</v>
       </c>
       <c r="F37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1387461459403904E-3</v>
       </c>
       <c r="G37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4665981500513875E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <f t="shared" si="5"/>
+        <v>0.63366336633663367</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="6"/>
+        <v>0.24752475247524752</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="7"/>
+        <v>0.11881188118811881</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>66</v>
       </c>
@@ -1778,19 +2259,31 @@
         <v>13</v>
       </c>
       <c r="E38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2689867333205153E-2</v>
       </c>
       <c r="F38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9990386464141513E-3</v>
       </c>
       <c r="G38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4995193232070756E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <f t="shared" si="5"/>
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="7"/>
+        <v>0.12380952380952381</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>65</v>
       </c>
@@ -1801,19 +2294,31 @@
         <v>11</v>
       </c>
       <c r="E39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3206013815522145E-2</v>
       </c>
       <c r="F39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8760666395774076E-3</v>
       </c>
       <c r="G39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2348638764729785E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="6"/>
+        <v>0.24</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="7"/>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>66</v>
       </c>
@@ -1824,19 +2329,31 @@
         <v>13</v>
       </c>
       <c r="E40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2689867333205153E-2</v>
       </c>
       <c r="F40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9990386464141513E-3</v>
       </c>
       <c r="G40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4995193232070756E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <f t="shared" si="5"/>
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="7"/>
+        <v>0.12380952380952381</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>66</v>
       </c>
@@ -1847,19 +2364,31 @@
         <v>12</v>
       </c>
       <c r="E41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2878048780487804E-2</v>
       </c>
       <c r="F41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8780487804878049E-3</v>
       </c>
       <c r="G41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3414634146341463E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="7"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>65</v>
       </c>
@@ -1870,19 +2399,31 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.282051282051282E-2</v>
       </c>
       <c r="F42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1282051282051282E-3</v>
       </c>
       <c r="G42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5641025641025641E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>64</v>
       </c>
@@ -1893,19 +2434,31 @@
         <v>11</v>
       </c>
       <c r="E43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.321767864518794E-2</v>
       </c>
       <c r="F43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1631557207765383E-3</v>
       </c>
       <c r="G43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.271788517141677E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <f t="shared" si="5"/>
+        <v>0.64</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="7"/>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>68</v>
       </c>
@@ -1916,19 +2469,31 @@
         <v>13</v>
       </c>
       <c r="E44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.231437884824339E-2</v>
       </c>
       <c r="F44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8895327779789931E-3</v>
       </c>
       <c r="G44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3542194856935894E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <f t="shared" si="5"/>
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="7"/>
+        <v>0.12037037037037036</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>65</v>
       </c>
@@ -1939,19 +2504,31 @@
         <v>12</v>
       </c>
       <c r="E45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3015618742490988E-2</v>
       </c>
       <c r="F45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0060072086503806E-3</v>
       </c>
       <c r="G45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4028834601521826E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <f t="shared" si="5"/>
+        <v>0.63725490196078427</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="6"/>
+        <v>0.24509803921568626</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="7"/>
+        <v>0.11764705882352941</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>68</v>
       </c>
@@ -1962,19 +2539,31 @@
         <v>13</v>
       </c>
       <c r="E46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.231437884824339E-2</v>
       </c>
       <c r="F46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8895327779789931E-3</v>
       </c>
       <c r="G46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3542194856935894E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <f t="shared" si="5"/>
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="7"/>
+        <v>0.12037037037037036</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>65</v>
       </c>
@@ -1985,19 +2574,31 @@
         <v>13</v>
       </c>
       <c r="E47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2950787009364416E-2</v>
       </c>
       <c r="F47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9810719266786211E-3</v>
       </c>
       <c r="G47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5901574018728831E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f t="shared" si="5"/>
+        <v>0.6310679611650486</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="7"/>
+        <v>0.12621359223300971</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>67</v>
       </c>
@@ -2008,19 +2609,31 @@
         <v>12</v>
       </c>
       <c r="E48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2620079110943681E-2</v>
       </c>
       <c r="F48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.89734413260501E-3</v>
       </c>
       <c r="G48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.260312676586928E-3</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <f t="shared" si="5"/>
+        <v>0.63809523809523805</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="6"/>
+        <v>0.24761904761904763</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="7"/>
+        <v>0.11428571428571428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>66</v>
       </c>
@@ -2031,19 +2644,31 @@
         <v>11</v>
       </c>
       <c r="E49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2808072967203571E-2</v>
       </c>
       <c r="F49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.0456045022317098E-3</v>
       </c>
       <c r="G49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1346788278672618E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>0.25242718446601942</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="7"/>
+        <v>0.10679611650485436</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>65</v>
       </c>
@@ -2054,19 +2679,31 @@
         <v>13</v>
       </c>
       <c r="E50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2950787009364416E-2</v>
       </c>
       <c r="F50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9810719266786211E-3</v>
       </c>
       <c r="G50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5901574018728831E-3</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <f t="shared" si="5"/>
+        <v>0.6310679611650486</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="7"/>
+        <v>0.12621359223300971</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>66</v>
       </c>
@@ -2077,19 +2714,31 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2497633024048476E-2</v>
       </c>
       <c r="F51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1126680552925586E-3</v>
       </c>
       <c r="G51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6510130657072524E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <f t="shared" si="5"/>
+        <v>0.61682242990654201</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="7"/>
+        <v>0.13084112149532709</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>68</v>
       </c>
@@ -2100,19 +2749,31 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2254460263110471E-2</v>
       </c>
       <c r="F52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8657415750585692E-3</v>
       </c>
       <c r="G52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5229771129933322E-3</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <f t="shared" si="5"/>
+        <v>0.62385321100917435</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="6"/>
+        <v>0.24770642201834864</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="7"/>
+        <v>0.12844036697247707</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>67</v>
       </c>
@@ -2123,19 +2784,31 @@
         <v>11</v>
       </c>
       <c r="E53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2674990541051836E-2</v>
       </c>
       <c r="F53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9186530457813087E-3</v>
       </c>
       <c r="G53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.0809685962920924E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <f t="shared" si="5"/>
+        <v>0.64423076923076927</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="7"/>
+        <v>0.10576923076923077</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>63</v>
       </c>
@@ -2146,19 +2819,31 @@
         <v>11</v>
       </c>
       <c r="E54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.321863197650021E-2</v>
       </c>
       <c r="F54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.4553084347461183E-3</v>
       </c>
       <c r="G54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3080151070079733E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <f t="shared" si="5"/>
+        <v>0.63</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="6"/>
+        <v>0.26</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="7"/>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>66</v>
       </c>
@@ -2169,19 +2854,31 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2748696156074947E-2</v>
       </c>
       <c r="F55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8290515742708132E-3</v>
       </c>
       <c r="G55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7042688815916553E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <f t="shared" si="5"/>
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="6"/>
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="7"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>66</v>
       </c>
@@ -2192,19 +2889,31 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2497633024048476E-2</v>
       </c>
       <c r="F56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1126680552925586E-3</v>
       </c>
       <c r="G56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6510130657072524E-3</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <f t="shared" si="5"/>
+        <v>0.61682242990654201</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="6"/>
+        <v>0.25233644859813081</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="7"/>
+        <v>0.13084112149532709</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>66</v>
       </c>
@@ -2215,19 +2924,31 @@
         <v>15</v>
       </c>
       <c r="E57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2429378531073447E-2</v>
       </c>
       <c r="F57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.084745762711864E-3</v>
       </c>
       <c r="G57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.8248587570621469E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <f t="shared" si="5"/>
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="7"/>
+        <v>0.1388888888888889</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>66</v>
       </c>
@@ -2238,19 +2959,31 @@
         <v>12</v>
       </c>
       <c r="E58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2878048780487804E-2</v>
       </c>
       <c r="F58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8780487804878049E-3</v>
       </c>
       <c r="G58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3414634146341463E-3</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="6"/>
+        <v>0.24271844660194175</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="7"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>66</v>
       </c>
@@ -2261,19 +2994,31 @@
         <v>13</v>
       </c>
       <c r="E59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.293863948245442E-2</v>
       </c>
       <c r="F59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7049598118016076E-3</v>
       </c>
       <c r="G59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5485198980592042E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <f t="shared" si="5"/>
+        <v>0.64077669902912626</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="6"/>
+        <v>0.23300970873786409</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="7"/>
+        <v>0.12621359223300971</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>70</v>
       </c>
@@ -2284,19 +3029,31 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2127512127512128E-2</v>
       </c>
       <c r="F60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.5045045045045045E-3</v>
       </c>
       <c r="G60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4255024255024253E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <f t="shared" si="5"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="6"/>
+        <v>0.23636363636363636</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="7"/>
+        <v>0.12727272727272726</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>68</v>
       </c>
@@ -2307,19 +3064,31 @@
         <v>15</v>
       </c>
       <c r="E61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2190749372534958E-2</v>
       </c>
       <c r="F61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8404446038006451E-3</v>
       </c>
       <c r="G61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6891358910003586E-3</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <f t="shared" si="5"/>
+        <v>0.61818181818181817</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="6"/>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="7"/>
+        <v>0.13636363636363635</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>69</v>
       </c>
@@ -2330,19 +3099,31 @@
         <v>13</v>
       </c>
       <c r="E62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2308241170174813E-2</v>
       </c>
       <c r="F62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.6378879771673204E-3</v>
       </c>
       <c r="G62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3189439885836602E-3</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <f t="shared" si="5"/>
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>0.24074074074074073</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="7"/>
+        <v>0.12037037037037036</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>70</v>
       </c>
@@ -2353,19 +3134,31 @@
         <v>15</v>
       </c>
       <c r="E63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1957635804578067E-2</v>
       </c>
       <c r="F63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.6122309531943968E-3</v>
       </c>
       <c r="G63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5623505295524428E-3</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="6"/>
+        <v>0.24107142857142858</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="7"/>
+        <v>0.13392857142857142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>69</v>
       </c>
@@ -2376,19 +3169,31 @@
         <v>15</v>
       </c>
       <c r="E64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2297273213330956E-2</v>
       </c>
       <c r="F64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.4555337729459991E-3</v>
       </c>
       <c r="G64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6733202637675992E-3</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <f t="shared" si="5"/>
+        <v>0.6330275229357798</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="6"/>
+        <v>0.22935779816513763</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="7"/>
+        <v>0.13761467889908258</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>69</v>
       </c>
@@ -2399,19 +3204,31 @@
         <v>15</v>
       </c>
       <c r="E65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2073490813648294E-2</v>
       </c>
       <c r="F65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7244094488188976E-3</v>
       </c>
       <c r="G65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6246719160104987E-3</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <f t="shared" si="5"/>
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="6"/>
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="7"/>
+        <v>0.13513513513513514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>69</v>
       </c>
@@ -2422,19 +3239,31 @@
         <v>16</v>
       </c>
       <c r="E66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2008353637312914E-2</v>
       </c>
       <c r="F66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.6989209885137488E-3</v>
       </c>
       <c r="G66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7845457709711106E-3</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <f t="shared" si="5"/>
+        <v>0.6160714285714286</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="6"/>
+        <v>0.24107142857142858</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2445,19 +3274,31 @@
         <v>18</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E87" si="5">A67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="E67:E87" si="10">A67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>1.2557077625570776E-2</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F87" si="6">B67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="F67:F87" si="11">B67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>4.5662100456621002E-3</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G87" si="7">C67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="G67:G87" si="12">C67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>3.4246575342465752E-3</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <f t="shared" ref="I67:I87" si="13">A67/($A67+$B67+$C67)</f>
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J87" si="14">B67/($A67+$B67+$C67)</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K87" si="15">C67/($A67+$B67+$C67)</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2468,19 +3309,31 @@
         <v>12</v>
       </c>
       <c r="E68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2862353618736801E-2</v>
       </c>
       <c r="F68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.6074102514878099E-3</v>
       </c>
       <c r="G68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.3037051257439049E-3</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <f t="shared" si="13"/>
+        <v>0.65048543689320393</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="14"/>
+        <v>0.23300970873786409</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="15"/>
+        <v>0.11650485436893204</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2491,19 +3344,31 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2617702448210923E-2</v>
       </c>
       <c r="F69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7080979284369112E-3</v>
       </c>
       <c r="G69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6365348399246705E-3</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <f t="shared" si="13"/>
+        <v>0.63207547169811318</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="14"/>
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="15"/>
+        <v>0.13207547169811321</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2514,19 +3379,31 @@
         <v>15</v>
       </c>
       <c r="E70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2307692307692308E-2</v>
       </c>
       <c r="F70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7058823529411761E-3</v>
       </c>
       <c r="G70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.7149321266968325E-3</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <f t="shared" si="13"/>
+        <v>0.62385321100917435</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="14"/>
+        <v>0.23853211009174313</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="15"/>
+        <v>0.13761467889908258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>68</v>
       </c>
@@ -2537,19 +3414,31 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2372634643377001E-2</v>
       </c>
       <c r="F71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7307132459970891E-3</v>
       </c>
       <c r="G71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.5473071324599709E-3</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <f t="shared" si="13"/>
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="14"/>
+        <v>0.24074074074074073</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="15"/>
+        <v>0.12962962962962962</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>68</v>
       </c>
@@ -2560,19 +3449,31 @@
         <v>15</v>
       </c>
       <c r="E72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2534562211981567E-2</v>
       </c>
       <c r="F72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.423963133640553E-3</v>
       </c>
       <c r="G72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.7649769585253456E-3</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <f t="shared" si="13"/>
+        <v>0.63551401869158874</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="14"/>
+        <v>0.22429906542056074</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="15"/>
+        <v>0.14018691588785046</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>67</v>
       </c>
@@ -2583,19 +3484,31 @@
         <v>13</v>
       </c>
       <c r="E73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2800917080626672E-2</v>
       </c>
       <c r="F73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.5854031333588076E-3</v>
       </c>
       <c r="G73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.4837600305693541E-3</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <f t="shared" si="13"/>
+        <v>0.64423076923076927</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="14"/>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>69</v>
       </c>
@@ -2606,19 +3519,31 @@
         <v>15</v>
       </c>
       <c r="E74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2073490813648294E-2</v>
       </c>
       <c r="F74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7244094488188976E-3</v>
       </c>
       <c r="G74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6246719160104987E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <f t="shared" si="13"/>
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="14"/>
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="15"/>
+        <v>0.13513513513513514</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>70</v>
       </c>
@@ -2629,19 +3554,31 @@
         <v>15</v>
       </c>
       <c r="E75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.1957635804578067E-2</v>
       </c>
       <c r="F75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.6122309531943968E-3</v>
       </c>
       <c r="G75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.5623505295524428E-3</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <f t="shared" si="13"/>
+        <v>0.625</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="14"/>
+        <v>0.24107142857142858</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="15"/>
+        <v>0.13392857142857142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>67</v>
       </c>
@@ -2652,19 +3589,31 @@
         <v>15</v>
       </c>
       <c r="E76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2430426716141002E-2</v>
       </c>
       <c r="F76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.8237476808905382E-3</v>
       </c>
       <c r="G76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.7829313543599257E-3</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <f t="shared" si="13"/>
+        <v>0.62037037037037035</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="14"/>
+        <v>0.24074074074074073</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="15"/>
+        <v>0.1388888888888889</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>67</v>
       </c>
@@ -2675,19 +3624,31 @@
         <v>15</v>
       </c>
       <c r="E77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2549166510582506E-2</v>
       </c>
       <c r="F77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.6825248173815318E-3</v>
       </c>
       <c r="G77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.8095148904289193E-3</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <f t="shared" si="13"/>
+        <v>0.62616822429906538</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="14"/>
+        <v>0.23364485981308411</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="15"/>
+        <v>0.14018691588785046</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>69</v>
       </c>
@@ -2698,19 +3659,31 @@
         <v>15</v>
       </c>
       <c r="E78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2073490813648294E-2</v>
       </c>
       <c r="F78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7244094488188976E-3</v>
       </c>
       <c r="G78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6246719160104987E-3</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <f t="shared" si="13"/>
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="14"/>
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="15"/>
+        <v>0.13513513513513514</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>70</v>
       </c>
@@ -2721,19 +3694,31 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2127512127512128E-2</v>
       </c>
       <c r="F79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.5045045045045045E-3</v>
       </c>
       <c r="G79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.4255024255024253E-3</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <f t="shared" si="13"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="14"/>
+        <v>0.23636363636363636</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="15"/>
+        <v>0.12727272727272726</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>68</v>
       </c>
@@ -2744,19 +3729,31 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2488521579430671E-2</v>
       </c>
       <c r="F80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.5913682277318639E-3</v>
       </c>
       <c r="G80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.5711662075298437E-3</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <f t="shared" si="13"/>
+        <v>0.63551401869158874</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="14"/>
+        <v>0.23364485981308411</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="15"/>
+        <v>0.13084112149532709</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>70</v>
       </c>
@@ -2767,19 +3764,31 @@
         <v>16</v>
       </c>
       <c r="E81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.1784511784511785E-2</v>
       </c>
       <c r="F81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7138047138047135E-3</v>
       </c>
       <c r="G81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6936026936026937E-3</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <f t="shared" si="13"/>
+        <v>0.61403508771929827</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="14"/>
+        <v>0.24561403508771928</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="15"/>
+        <v>0.14035087719298245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>69</v>
       </c>
@@ -2790,19 +3799,31 @@
         <v>15</v>
       </c>
       <c r="E82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2073490813648294E-2</v>
       </c>
       <c r="F82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7244094488188976E-3</v>
       </c>
       <c r="G82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6246719160104987E-3</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <f t="shared" si="13"/>
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="14"/>
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="15"/>
+        <v>0.13513513513513514</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>71</v>
       </c>
@@ -2813,19 +3834,31 @@
         <v>15</v>
       </c>
       <c r="E83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.1843202668890742E-2</v>
       </c>
       <c r="F83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.5037531276063388E-3</v>
       </c>
       <c r="G83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.5020850708924102E-3</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <f t="shared" si="13"/>
+        <v>0.62831858407079644</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="14"/>
+        <v>0.23893805309734514</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="15"/>
+        <v>0.13274336283185842</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>69</v>
       </c>
@@ -2836,19 +3869,31 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2249245517486242E-2</v>
       </c>
       <c r="F84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.6156577312266994E-3</v>
       </c>
       <c r="G84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.4853541629682231E-3</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <f t="shared" si="13"/>
+        <v>0.6330275229357798</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="14"/>
+        <v>0.23853211009174313</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="15"/>
+        <v>0.12844036697247707</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>70</v>
       </c>
@@ -2859,19 +3904,31 @@
         <v>18</v>
       </c>
       <c r="E85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.1758777087182933E-2</v>
       </c>
       <c r="F85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.5355283050562741E-3</v>
       </c>
       <c r="G85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>3.0236855367041827E-3</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <f t="shared" si="13"/>
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="14"/>
+        <v>0.23478260869565218</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="15"/>
+        <v>0.15652173913043479</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>69</v>
       </c>
@@ -2882,19 +3939,31 @@
         <v>15</v>
       </c>
       <c r="E86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2073490813648294E-2</v>
       </c>
       <c r="F86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7244094488188976E-3</v>
       </c>
       <c r="G86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6246719160104987E-3</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <f t="shared" si="13"/>
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="14"/>
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="15"/>
+        <v>0.13513513513513514</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>67</v>
       </c>
@@ -2905,16 +3974,28 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2617702448210923E-2</v>
       </c>
       <c r="F87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>4.7080979284369112E-3</v>
       </c>
       <c r="G87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>2.6365348399246705E-3</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="13"/>
+        <v>0.63207547169811318</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="14"/>
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="15"/>
+        <v>0.13207547169811321</v>
       </c>
     </row>
   </sheetData>
